--- a/artfynd/A 31086-2026 artfynd.xlsx
+++ b/artfynd/A 31086-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136149918</v>
       </c>
       <c r="B2" t="n">
-        <v>89468</v>
+        <v>89470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136149927</v>
       </c>
       <c r="B3" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31086-2026 artfynd.xlsx
+++ b/artfynd/A 31086-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136149927</v>
       </c>
       <c r="B3" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31086-2026 artfynd.xlsx
+++ b/artfynd/A 31086-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136149918</v>
       </c>
       <c r="B2" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136149927</v>
       </c>
       <c r="B3" t="n">
-        <v>92102</v>
+        <v>92107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136149903</v>
       </c>
       <c r="B4" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136149905</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136149907</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136149911</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136149912</v>
       </c>
       <c r="B8" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136149915</v>
       </c>
       <c r="B9" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>136149938</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>136149944</v>
       </c>
       <c r="B11" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>136149945</v>
       </c>
       <c r="B12" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136149948</v>
       </c>
       <c r="B13" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>136149952</v>
       </c>
       <c r="B14" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136149953</v>
       </c>
       <c r="B15" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>136149954</v>
       </c>
       <c r="B16" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>136149906</v>
       </c>
       <c r="B17" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>136149917</v>
       </c>
       <c r="B18" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>136149919</v>
       </c>
       <c r="B19" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>136149920</v>
       </c>
       <c r="B20" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136149926</v>
       </c>
       <c r="B21" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>136149928</v>
       </c>
       <c r="B22" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>136149933</v>
       </c>
       <c r="B23" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>136149934</v>
       </c>
       <c r="B24" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136149937</v>
       </c>
       <c r="B25" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>136149955</v>
       </c>
       <c r="B26" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
